--- a/delivery130/03_Excel_Deliveries/8_Artist_Master_List.xlsx
+++ b/delivery130/03_Excel_Deliveries/8_Artist_Master_List.xlsx
@@ -472,7 +472,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28. Source: delivery130/04_Datasets — figures equal those cells.</t>
+          <t>Generated 2026-08-31. Source: delivery130/04_Datasets — figures equal those cells.</t>
         </is>
       </c>
     </row>

--- a/delivery130/03_Excel_Deliveries/8_Artist_Master_List.xlsx
+++ b/delivery130/03_Excel_Deliveries/8_Artist_Master_List.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Artist_Master_List" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artist_Master_List'!$A$1:$H$131</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Artist_Master_List'!$A$1:$H$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artist_Master_List'!$A$1:$H$130</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Artist_Master_List'!$A$1:$H$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,14 +465,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Scope: 130 artists (first-submission cohort) x 31 quarters, Q1 2019 – Q3 2026</t>
+          <t>Scope: 129 artists (first-submission cohort) x 31 quarters, Q1 2019 – Q3 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-31. Source: delivery130/04_Datasets — figures equal those cells.</t>
+          <t>Generated 2026-09-01. Source: delivery130/04_Datasets — figures equal those cells.</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>130 rows, one per artist. The first submission's list held 131 rows because "Flavour" and "Flavour N'abania" are the same artist under two provider UUIDs; they are one row here.</t>
+          <t>129 rows, one per artist. The first submission's list held 131 rows because "Flavour" and "Flavour N'abania" are the same artist under two provider UUIDs; they are one row here.</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2306,11 +2306,11 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1439568</v>
+        <v>11587</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Odunsi</t>
+          <t>Odunsi (The Engine)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2330,11 +2330,11 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>11587</v>
+        <v>1103816</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Odunsi (The Engine)</t>
+          <t>Olakira</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2354,11 +2354,11 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1103816</v>
+        <v>5061</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Olakira</t>
+          <t>Olamide</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2378,11 +2378,11 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>5061</v>
+        <v>29054</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Olamide</t>
+          <t>Olu Maintain</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2402,11 +2402,11 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>29054</v>
+        <v>3578130</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Olu Maintain</t>
+          <t>Omah Lay</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2426,11 +2426,11 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3578130</v>
+        <v>3803802</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Omah Lay</t>
+          <t>Oritsefemi</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2450,11 +2450,11 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3803802</v>
+        <v>1373421</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Oritsefemi</t>
+          <t>Oxlade</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2474,11 +2474,11 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1373421</v>
+        <v>3740</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Oxlade</t>
+          <t>P-Square</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2498,11 +2498,11 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>3740</v>
+        <v>5321</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>P-Square</t>
+          <t>Patoranking</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2522,11 +2522,11 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5321</v>
+        <v>745195</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Patoranking</t>
+          <t>Peruzzi</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2546,11 +2546,11 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>745195</v>
+        <v>406946</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Peruzzi</t>
+          <t>Pheelz</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2570,11 +2570,11 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>406946</v>
+        <v>5012</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pheelz</t>
+          <t>Phyno</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2594,11 +2594,11 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>5012</v>
+        <v>8230229</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Phyno</t>
+          <t>Portable</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2618,11 +2618,11 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>8230229</v>
+        <v>310091</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Portable</t>
+          <t>Praiz</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2642,11 +2642,11 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>310091</v>
+        <v>918914</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Praiz</t>
+          <t>Prettyboy D-O</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2666,11 +2666,11 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>918914</v>
+        <v>9785228</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prettyboy D-O</t>
+          <t>Qing Madi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2690,11 +2690,11 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>9785228</v>
+        <v>237551</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Qing Madi</t>
+          <t>Reekado Banks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2714,11 +2714,11 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>237551</v>
+        <v>1426518</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Reekado Banks</t>
+          <t>Rema</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2738,11 +2738,11 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1426518</v>
+        <v>317357</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rema</t>
+          <t>Reminisce</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2762,11 +2762,11 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>317357</v>
+        <v>638877</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Reminisce</t>
+          <t>Ric Hassani</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2786,11 +2786,11 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>638877</v>
+        <v>1630426</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ric Hassani</t>
+          <t>Rude Boy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2810,11 +2810,11 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1630426</v>
+        <v>4198930</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Rude Boy</t>
+          <t>Ruger</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2834,11 +2834,11 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4198930</v>
+        <v>308113</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ruger</t>
+          <t>Sarz</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2858,11 +2858,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>308113</v>
+        <v>321148</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sarz</t>
+          <t>Sauce Kid</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2882,11 +2882,11 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>321148</v>
+        <v>203976</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sauce Kid</t>
+          <t>Sean Tizzle</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2906,11 +2906,11 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>203976</v>
+        <v>39092</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sean Tizzle</t>
+          <t>Seyi Shay</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2930,11 +2930,11 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>39092</v>
+        <v>1637455</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Seyi Shay</t>
+          <t>Seyi Vibez</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2954,11 +2954,11 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1637455</v>
+        <v>6487237</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Seyi Vibez</t>
+          <t>Shallipopi</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2978,11 +2978,11 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>6487237</v>
+        <v>655429</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Shallipopi</t>
+          <t>Show Dem Camp</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3002,11 +3002,11 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>655429</v>
+        <v>374667</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Show Dem Camp</t>
+          <t>Simi</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3026,11 +3026,11 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>374667</v>
+        <v>680380</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Simi</t>
+          <t>Skiibii</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3050,11 +3050,11 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>680380</v>
+        <v>515515</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Skiibii</t>
+          <t>Small Doctor</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3074,11 +3074,11 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>515515</v>
+        <v>92994</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Small Doctor</t>
+          <t>Solidstar</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3098,11 +3098,11 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>92994</v>
+        <v>249694</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Solidstar</t>
+          <t>Sound Sultan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3122,11 +3122,11 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>249694</v>
+        <v>536112</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sound Sultan</t>
+          <t>Spyro</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3146,11 +3146,11 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>536112</v>
+        <v>565281</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Spyro</t>
+          <t>Tay Iwar</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3170,11 +3170,11 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>565281</v>
+        <v>426512</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tay Iwar</t>
+          <t>Tekno</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3194,11 +3194,11 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>426512</v>
+        <v>9190388</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tekno</t>
+          <t>Tempoe</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3218,11 +3218,11 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>9190388</v>
+        <v>1345060</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tempoe</t>
+          <t>Tems</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3242,11 +3242,11 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1345060</v>
+        <v>349654</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tems</t>
+          <t>Teni</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3266,11 +3266,11 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>349654</v>
+        <v>883093</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Teni</t>
+          <t>Terri</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3290,11 +3290,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>883093</v>
+        <v>228944</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Terri</t>
+          <t>Terry Apala</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3314,11 +3314,11 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>228944</v>
+        <v>210713</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Terry Apala</t>
+          <t>Timaya</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3338,11 +3338,11 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>210713</v>
+        <v>4686</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Timaya</t>
+          <t>Tiwa Savage</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3362,11 +3362,11 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>4686</v>
+        <v>170806</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tiwa Savage</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3386,11 +3386,11 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>170806</v>
+        <v>3905071</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Victony</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3410,11 +3410,11 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>3905071</v>
+        <v>429450</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Victony</t>
+          <t>Waje</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3434,11 +3434,11 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>429450</v>
+        <v>3499</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Waje</t>
+          <t>Wande Coal</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3458,11 +3458,11 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>3499</v>
+        <v>4390</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Wande Coal</t>
+          <t>Wizkid</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3482,11 +3482,11 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>4390</v>
+        <v>424613</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Wizkid</t>
+          <t>WurlD</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3506,11 +3506,11 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>424613</v>
+        <v>5382</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>WurlD</t>
+          <t>Ycee</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3530,11 +3530,11 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>5382</v>
+        <v>211381</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ycee</t>
+          <t>Yemi Alade</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3554,11 +3554,11 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>211381</v>
+        <v>1186093</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Yemi Alade</t>
+          <t>Young Jonn</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3578,11 +3578,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1186093</v>
+        <v>5060</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Young Jonn</t>
+          <t>Yung6ix</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3602,11 +3602,11 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>5060</v>
+        <v>1582294</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Yung6ix</t>
+          <t>Zinoleesky</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3626,11 +3626,11 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1582294</v>
+        <v>392233</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Zinoleesky</t>
+          <t>Zlatan</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3648,32 +3648,8 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>392233</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Zlatan</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>NG</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H131"/>
+  <autoFilter ref="A1:H130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
